--- a/data/Lüterkofen-Ichertswil/investment_decision/Ichertswil_SFH_2005-2014_investment_decision.xlsx
+++ b/data/Lüterkofen-Ichertswil/investment_decision/Ichertswil_SFH_2005-2014_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>9.677197915912732</v>
+        <v>7.658896701479595</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,19 +508,19 @@
         <v>2477.355633491832</v>
       </c>
       <c r="F2" t="n">
-        <v>9.677197915912732</v>
+        <v>7.658896701479595</v>
       </c>
       <c r="G2" t="n">
         <v>2477.355633491832</v>
       </c>
       <c r="H2" t="n">
-        <v>9.677197915912732</v>
+        <v>7.658896701479595</v>
       </c>
       <c r="I2" t="n">
         <v>2477.355633491832</v>
       </c>
       <c r="J2" t="n">
-        <v>9.677197915912732</v>
+        <v>7.658896701479595</v>
       </c>
       <c r="K2" t="n">
         <v>2477.355633491832</v>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>17.38662932697595</v>
+        <v>10.15943708541559</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>2477.355633491832</v>
       </c>
       <c r="F3" t="n">
-        <v>17.46023996537312</v>
+        <v>10.03352017505804</v>
       </c>
       <c r="G3" t="n">
         <v>2477.355633491832</v>
       </c>
       <c r="H3" t="n">
-        <v>14.57571027843527</v>
+        <v>10.42378590041761</v>
       </c>
       <c r="I3" t="n">
         <v>2477.355633491832</v>
       </c>
       <c r="J3" t="n">
-        <v>15.84739219567892</v>
+        <v>10.03352017505804</v>
       </c>
       <c r="K3" t="n">
         <v>2477.355633491832</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>17.38662932697595</v>
+        <v>10.15943708541559</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>2477.355633491832</v>
       </c>
       <c r="F4" t="n">
-        <v>17.46023996537312</v>
+        <v>10.60422822184818</v>
       </c>
       <c r="G4" t="n">
         <v>2477.355633491832</v>
       </c>
       <c r="H4" t="n">
-        <v>14.57571027843527</v>
+        <v>10.42378590041761</v>
       </c>
       <c r="I4" t="n">
         <v>2477.355633491832</v>
       </c>
       <c r="J4" t="n">
-        <v>15.84739219567892</v>
+        <v>10.60422822184819</v>
       </c>
       <c r="K4" t="n">
         <v>2477.355633491832</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>18.21279282417338</v>
+        <v>10.15943708541559</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>2477.355633491832</v>
       </c>
       <c r="F5" t="n">
-        <v>17.4956245023219</v>
+        <v>10.60422822184818</v>
       </c>
       <c r="G5" t="n">
         <v>2477.355633491832</v>
       </c>
       <c r="H5" t="n">
-        <v>14.57571027843527</v>
+        <v>10.42378590041761</v>
       </c>
       <c r="I5" t="n">
         <v>2477.355633491832</v>
       </c>
       <c r="J5" t="n">
-        <v>15.84739219567892</v>
+        <v>10.60422822184819</v>
       </c>
       <c r="K5" t="n">
         <v>2477.355633491832</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>18.21279282417338</v>
+        <v>15.77547523114781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>2477.355633491832</v>
       </c>
       <c r="F6" t="n">
-        <v>17.4956245023219</v>
+        <v>15.77547523114779</v>
       </c>
       <c r="G6" t="n">
         <v>2477.355633491832</v>
       </c>
       <c r="H6" t="n">
-        <v>14.57571027843527</v>
+        <v>15.77547523114779</v>
       </c>
       <c r="I6" t="n">
         <v>2477.355633491832</v>
       </c>
       <c r="J6" t="n">
-        <v>15.84739219567892</v>
+        <v>15.7754752311478</v>
       </c>
       <c r="K6" t="n">
         <v>2477.355633491832</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>3.716033450237748</v>
+        <v>5.457923595505617</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.716033450237748</v>
+        <v>5.457923595505617</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1.98242009448871</v>
+        <v>2.91167922862001</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.98242009448871</v>
+        <v>2.91167922862001</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>3.716033450237748</v>
+        <v>5.457923595505617</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.716033450237748</v>
+        <v>5.457923595505617</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.606947344824408</v>
+        <v>3.828953537715741</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.606947344824408</v>
+        <v>3.828953537715741</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>3.716033450237748</v>
+        <v>5.457923595505617</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.716033450237748</v>
+        <v>5.457923595505617</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.896571630457768</v>
+        <v>4.254339165578869</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.896571630457768</v>
+        <v>4.254339165578869</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>3.716033450237748</v>
+        <v>5.457923595505617</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>3.716033450237748</v>
+        <v>5.457923595505617</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3.059982732835629</v>
+        <v>4.49434919869056</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3.059982732835629</v>
+        <v>4.49434919869056</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>3.716033450237748</v>
+        <v>5.457923595505617</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3.716033450237748</v>
+        <v>5.457923595505617</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3.164114059271456</v>
+        <v>4.64729206941446</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>3.164114059271456</v>
+        <v>4.64729206941446</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.00093161120160247</v>
+        <v>0.0008082313411764706</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0009316112016024702</v>
+        <v>0.0008082313411764707</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0009316112016024702</v>
+        <v>0.0008082313411764707</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0009316112016024702</v>
+        <v>0.0008082313411764706</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00093161120160247</v>
+        <v>0.0008082313411764707</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0009316112016024702</v>
+        <v>0.0008082313411764707</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0009316112016024702</v>
+        <v>0.0008082313411764706</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0009316112016024702</v>
+        <v>0.0008082313411764706</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.00093161120160247</v>
+        <v>0.0008082313411764707</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0009316112016024702</v>
+        <v>0.0008082313411764706</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0009316112016024702</v>
+        <v>0.0008082313411764707</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0009316112016024702</v>
+        <v>0.0008082313411764706</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0009919202823529412</v>
+        <v>0.0008082313411764707</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0009919202823529412</v>
+        <v>0.0008082313411764707</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0009919202823529412</v>
+        <v>0.0008082313411764707</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0009919202823529412</v>
+        <v>0.0008082313411764707</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0009919202823529412</v>
+        <v>0.0008082313411764707</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0009919202823529412</v>
+        <v>0.0008082313411764706</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0009919202823529412</v>
+        <v>0.0008082313411764707</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0009919202823529412</v>
+        <v>0.0008082313411764707</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.03203919914868786</v>
+        <v>0.1782818493251058</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1063,19 +1063,19 @@
         <v>0.65576952</v>
       </c>
       <c r="F17" t="n">
-        <v>0.03203919914868784</v>
+        <v>0.1792965500000005</v>
       </c>
       <c r="G17" t="n">
         <v>0.65576952</v>
       </c>
       <c r="H17" t="n">
-        <v>0.03203919914868784</v>
+        <v>0.173511312735875</v>
       </c>
       <c r="I17" t="n">
         <v>0.65576952</v>
       </c>
       <c r="J17" t="n">
-        <v>0.03203919914868784</v>
+        <v>0.1724818514214167</v>
       </c>
       <c r="K17" t="n">
         <v>0.65576952</v>
@@ -1086,7 +1086,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.03203919914868786</v>
+        <v>0.1782818493251059</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,19 +1100,19 @@
         <v>0.65576952</v>
       </c>
       <c r="F18" t="n">
-        <v>0.03203919914868784</v>
+        <v>0.1792965500000005</v>
       </c>
       <c r="G18" t="n">
         <v>0.65576952</v>
       </c>
       <c r="H18" t="n">
-        <v>0.03203919914868784</v>
+        <v>0.173511312735875</v>
       </c>
       <c r="I18" t="n">
         <v>0.65576952</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03203919914868784</v>
+        <v>0.1724818514214167</v>
       </c>
       <c r="K18" t="n">
         <v>0.65576952</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.03203919914868786</v>
+        <v>0.1782818493251059</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>0.65576952</v>
       </c>
       <c r="F19" t="n">
-        <v>0.03203919914868784</v>
+        <v>0.1792965500000005</v>
       </c>
       <c r="G19" t="n">
         <v>0.65576952</v>
       </c>
       <c r="H19" t="n">
-        <v>0.03203919914868784</v>
+        <v>0.173511312735875</v>
       </c>
       <c r="I19" t="n">
         <v>0.65576952</v>
       </c>
       <c r="J19" t="n">
-        <v>0.03203919914868784</v>
+        <v>0.1724818514214167</v>
       </c>
       <c r="K19" t="n">
         <v>0.65576952</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.17565255</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>0.65576952</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.1747462007953188</v>
       </c>
       <c r="G20" t="n">
         <v>0.65576952</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.1083799061008803</v>
       </c>
       <c r="I20" t="n">
         <v>0.65576952</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.1074974300271694</v>
       </c>
       <c r="K20" t="n">
         <v>0.65576952</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.17565255</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>0.65576952</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.1747462007953188</v>
       </c>
       <c r="G21" t="n">
         <v>0.65576952</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.1083799061008803</v>
       </c>
       <c r="I21" t="n">
         <v>0.65576952</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.1074974300271694</v>
       </c>
       <c r="K21" t="n">
         <v>0.65576952</v>
@@ -1476,13 +1476,13 @@
         <v>0.65576952</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.01664643986962228</v>
       </c>
       <c r="I28" t="n">
         <v>0.65576952</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.018515133818262</v>
       </c>
       <c r="K28" t="n">
         <v>0.65576952</v>
@@ -1513,13 +1513,13 @@
         <v>0.65576952</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.01965943989934236</v>
       </c>
       <c r="I29" t="n">
         <v>0.65576952</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.01951694999999997</v>
       </c>
       <c r="K29" t="n">
         <v>0.65576952</v>
@@ -1550,13 +1550,13 @@
         <v>0.65576952</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.03903389999999998</v>
       </c>
       <c r="I30" t="n">
         <v>0.65576952</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.03903389999999998</v>
       </c>
       <c r="K30" t="n">
         <v>0.65576952</v>
@@ -1587,13 +1587,13 @@
         <v>0.65576952</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.0223874601303777</v>
       </c>
       <c r="I31" t="n">
         <v>0.65576952</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.02051876618173799</v>
       </c>
       <c r="K31" t="n">
         <v>0.65576952</v>
@@ -2381,7 +2381,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.2305448688246644</v>
+        <v>0.2055644154772301</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2395,19 +2395,19 @@
         <v>3.427670217060343</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1930704332952477</v>
+        <v>0.1863707779253736</v>
       </c>
       <c r="G53" t="n">
         <v>3.427670217060343</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1844527370469922</v>
+        <v>0.1970530241706709</v>
       </c>
       <c r="I53" t="n">
         <v>1.429189408046993</v>
       </c>
       <c r="J53" t="n">
-        <v>0.2165067427935359</v>
+        <v>0.1863707779253736</v>
       </c>
       <c r="K53" t="n">
         <v>1.429189408046993</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>1.196494064489334</v>
+        <v>1.185269611541574</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>3.427670217060343</v>
       </c>
       <c r="F54" t="n">
-        <v>1.178030604099433</v>
+        <v>1.156372419623195</v>
       </c>
       <c r="G54" t="n">
         <v>3.427670217060343</v>
       </c>
       <c r="H54" t="n">
-        <v>1.166083842929345</v>
+        <v>1.182961296825177</v>
       </c>
       <c r="I54" t="n">
         <v>1.668935448423029</v>
       </c>
       <c r="J54" t="n">
-        <v>1.194135649927367</v>
+        <v>1.156372419623196</v>
       </c>
       <c r="K54" t="n">
         <v>1.668935448423029</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>1.196494064489334</v>
+        <v>1.185269611541574</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>3.427670217060343</v>
       </c>
       <c r="F55" t="n">
-        <v>1.178030604099433</v>
+        <v>1.156372419623195</v>
       </c>
       <c r="G55" t="n">
         <v>3.427670217060343</v>
       </c>
       <c r="H55" t="n">
-        <v>1.166083842929345</v>
+        <v>1.182961296825177</v>
       </c>
       <c r="I55" t="n">
         <v>1.816517451088853</v>
       </c>
       <c r="J55" t="n">
-        <v>1.194135649927367</v>
+        <v>1.156372419623196</v>
       </c>
       <c r="K55" t="n">
         <v>1.816517451088853</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>1.193433361076083</v>
+        <v>1.195498769004392</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>3.427670217060343</v>
       </c>
       <c r="F56" t="n">
-        <v>1.071509643623738</v>
+        <v>1.170074373787254</v>
       </c>
       <c r="G56" t="n">
         <v>3.427670217060343</v>
       </c>
       <c r="H56" t="n">
-        <v>1.027910184582127</v>
+        <v>1.17349155741668</v>
       </c>
       <c r="I56" t="n">
         <v>1.915623816661862</v>
       </c>
       <c r="J56" t="n">
-        <v>1.178260176885986</v>
+        <v>1.146845036214569</v>
       </c>
       <c r="K56" t="n">
         <v>1.915623816661862</v>
@@ -2714,7 +2714,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>0.4408664111698575</v>
+        <v>0</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2728,19 +2728,19 @@
         <v>3.427670217060343</v>
       </c>
       <c r="F62" t="n">
-        <v>0.4408664111698575</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>3.427670217060343</v>
       </c>
       <c r="H62" t="n">
-        <v>0.4408664111698574</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>3.427670217060343</v>
       </c>
       <c r="J62" t="n">
-        <v>0.4408664111698574</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
         <v>3.427670217060343</v>
@@ -2751,7 +2751,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.6323836820073958</v>
+        <v>0.3082370814217136</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2765,19 +2765,19 @@
         <v>3.427670217060343</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6682343534545219</v>
+        <v>0.3286136302439807</v>
       </c>
       <c r="G63" t="n">
         <v>3.427670217060343</v>
       </c>
       <c r="H63" t="n">
-        <v>0.7404813810322886</v>
+        <v>0.3142650795787937</v>
       </c>
       <c r="I63" t="n">
         <v>3.427670217060343</v>
       </c>
       <c r="J63" t="n">
-        <v>0.6803755682877234</v>
+        <v>0.3286136302439807</v>
       </c>
       <c r="K63" t="n">
         <v>3.427670217060343</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.6664344863427257</v>
+        <v>0.3285318853573703</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>3.427670217060343</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6832741826503365</v>
+        <v>0.3532505404392677</v>
       </c>
       <c r="G64" t="n">
         <v>3.427670217060343</v>
       </c>
       <c r="H64" t="n">
-        <v>0.7588502751499365</v>
+        <v>0.3283568069242871</v>
       </c>
       <c r="I64" t="n">
         <v>3.427670217060343</v>
       </c>
       <c r="J64" t="n">
-        <v>0.7027466611538928</v>
+        <v>0.3532505404392682</v>
       </c>
       <c r="K64" t="n">
         <v>3.427670217060343</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.648210291551606</v>
+        <v>0.3285318853573703</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>3.427670217060343</v>
       </c>
       <c r="F65" t="n">
-        <v>0.6824936413941135</v>
+        <v>0.3532505404392677</v>
       </c>
       <c r="G65" t="n">
         <v>3.427670217060343</v>
       </c>
       <c r="H65" t="n">
-        <v>0.7588502751499365</v>
+        <v>0.3283568069242871</v>
       </c>
       <c r="I65" t="n">
         <v>3.427670217060343</v>
       </c>
       <c r="J65" t="n">
-        <v>0.7027466611538928</v>
+        <v>0.3532505404392682</v>
       </c>
       <c r="K65" t="n">
         <v>3.427670217060343</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.7470127707373267</v>
+        <v>0.2655435329716663</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>3.427670217060343</v>
       </c>
       <c r="F66" t="n">
-        <v>0.8847563776422775</v>
+        <v>0.2909679281888041</v>
       </c>
       <c r="G66" t="n">
         <v>3.427670217060343</v>
       </c>
       <c r="H66" t="n">
-        <v>0.9927657092696232</v>
+        <v>0.2875507445593781</v>
       </c>
       <c r="I66" t="n">
         <v>3.427670217060343</v>
       </c>
       <c r="J66" t="n">
-        <v>0.8143639099677424</v>
+        <v>0.3141972657614888</v>
       </c>
       <c r="K66" t="n">
         <v>3.427670217060343</v>
@@ -3107,13 +3107,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.07493215476634227</v>
+        <v>3.427670217060343</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.07493215476634227</v>
+        <v>3.427670217060343</v>
       </c>
     </row>
     <row r="73">
@@ -3144,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1305914202985151</v>
+        <v>3.427670217060343</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.1305914202985151</v>
+        <v>3.427670217060343</v>
       </c>
     </row>
     <row r="74">
@@ -3181,13 +3181,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.176667013297137</v>
+        <v>3.427670217060343</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.176667013297137</v>
+        <v>3.427670217060343</v>
       </c>
     </row>
     <row r="75">
@@ -3218,13 +3218,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2161004142813164</v>
+        <v>3.427670217060343</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2161004142813164</v>
+        <v>3.427670217060343</v>
       </c>
     </row>
     <row r="76">
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2504452346069824</v>
+        <v>3.427670217060343</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.2504452346069824</v>
+        <v>3.427670217060343</v>
       </c>
     </row>
     <row r="77">
@@ -3292,13 +3292,13 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.07493215476634227</v>
+        <v>3.427670217060343</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.07493215476634227</v>
+        <v>3.427670217060343</v>
       </c>
     </row>
     <row r="78">
@@ -3329,13 +3329,13 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1305914202985151</v>
+        <v>3.427670217060343</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.1305914202985151</v>
+        <v>3.427670217060343</v>
       </c>
     </row>
     <row r="79">
@@ -3366,13 +3366,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0.176667013297137</v>
+        <v>3.427670217060343</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.176667013297137</v>
+        <v>3.427670217060343</v>
       </c>
     </row>
     <row r="80">
@@ -3403,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2161004142813164</v>
+        <v>3.427670217060343</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.2161004142813164</v>
+        <v>3.427670217060343</v>
       </c>
     </row>
     <row r="81">
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2504452346069824</v>
+        <v>3.427670217060343</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2504452346069824</v>
+        <v>3.427670217060343</v>
       </c>
     </row>
     <row r="82">
